--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -691,7 +691,6 @@
           <t>True</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -721,7 +720,6 @@
           <t>NEXTEND</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>5</t>
@@ -739,7 +737,6 @@
           <t>SIMDATA</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>False</t>
@@ -757,7 +754,6 @@
           <t>SCIDATA</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>True</t>
@@ -841,7 +837,6 @@
           <t>CREATOR</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Pandora MOC</t>
@@ -859,7 +854,6 @@
           <t>CRSOFTV</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>v3.08</t>
@@ -877,7 +871,6 @@
           <t>COMPTYPE</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>1</t>
@@ -895,7 +888,6 @@
           <t>TRANSID</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>0</t>
@@ -913,7 +905,6 @@
           <t>FILENAME</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>/sssp/data/2026/08/15/2026-08-15__00-16-39_VisSci_KELT-9b_d050_n005_f11916_e000200000us.sp</t>
@@ -931,7 +922,6 @@
           <t>BITDEPTH</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>32</t>
@@ -949,7 +939,6 @@
           <t>TARG_ID</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>KELT-9b</t>
@@ -967,7 +956,6 @@
           <t>TARG_RA</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>307.8599548339844</t>
@@ -985,7 +973,6 @@
           <t>TARG_DEC</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>39.9389762878418</t>
@@ -1003,7 +990,6 @@
           <t>FRMSREQD</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>12250</t>
@@ -1021,7 +1007,6 @@
           <t>FRMSCLCT</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>11916</t>
@@ -1039,7 +1024,6 @@
           <t>NUMSTARS</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>5</t>
@@ -1057,7 +1041,6 @@
           <t>STARDIMS</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>50</t>
@@ -1075,7 +1058,6 @@
           <t>NUMPCOAD</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>238</t>
@@ -1093,7 +1075,6 @@
           <t>FRMPCOAD</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>50</t>
@@ -1111,7 +1092,6 @@
           <t>ROISTRTX</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>384</t>
@@ -1129,7 +1109,6 @@
           <t>ROISTRTY</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>384</t>
@@ -1147,7 +1126,6 @@
           <t>ROISIZEX</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>1280</t>
@@ -1165,7 +1143,6 @@
           <t>ROISIZEY</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>1280</t>
@@ -1183,7 +1160,6 @@
           <t>EXPTIME</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>200000</t>
@@ -1201,7 +1177,6 @@
           <t>RICEX</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>5</t>
@@ -1219,7 +1194,6 @@
           <t>RICEY</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>25</t>
@@ -1237,7 +1211,6 @@
           <t>CORRMODE</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>0</t>
@@ -1255,7 +1228,6 @@
           <t>CORSTIME</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>840068292</t>
@@ -1273,7 +1245,6 @@
           <t>FINETIME</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>8000000</t>
@@ -1291,7 +1262,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>7ZJPAXGM8XGMAXGM</t>
@@ -1309,7 +1279,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>0</t>
@@ -1327,13 +1296,11 @@
           <t>FIXED</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1341,13 +1308,11 @@
           <t>PFSOFTV</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>0.6.0</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1355,13 +1320,11 @@
           <t>PRSOFTV</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>2.9.1</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1369,13 +1332,11 @@
           <t>PFCLASS</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>VISDALevel1HDUList</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1383,7 +1344,6 @@
           <t>PFTIME</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>2026-09-09T19:39:20.989</t>
@@ -1503,13 +1463,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1517,13 +1475,11 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1531,13 +1487,11 @@
           <t>NAXIS3</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1545,7 +1499,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>0</t>
@@ -1563,7 +1516,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
@@ -1591,7 +1543,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1609,7 +1560,6 @@
           <t>2147483648</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1639,7 +1589,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>7ASq78Qo7AQo77Qo</t>
@@ -1657,7 +1606,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>2878043978</t>
@@ -1675,13 +1623,11 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>ct</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1791,7 +1737,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>42</t>
@@ -1809,7 +1754,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>5</t>
@@ -1827,7 +1771,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1845,7 +1788,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -1895,7 +1837,6 @@
           <t>StarROI_StartX</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1913,7 +1854,6 @@
           <t>I21</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1931,7 +1871,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1949,7 +1888,6 @@
           <t>StarROI_StartY</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1967,7 +1905,6 @@
           <t>I21</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1985,7 +1922,6 @@
           <t>22</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2015,7 +1951,6 @@
           <t>NUMSTARS</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>5</t>
@@ -2033,7 +1968,6 @@
           <t>STARDIMS</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>50</t>
@@ -2051,7 +1985,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>VNS2VKR1VKR1VKR1</t>
@@ -2069,7 +2002,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>17102079</t>
@@ -2189,7 +2121,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>219</t>
@@ -2207,7 +2138,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>11916</t>
@@ -2225,7 +2155,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -2243,7 +2172,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -2293,7 +2221,6 @@
           <t>ExposureStartTime_us</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2311,7 +2238,6 @@
           <t>I194</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2329,7 +2255,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2347,7 +2272,6 @@
           <t>Temperature</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2365,7 +2289,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2383,7 +2306,6 @@
           <t>195</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2413,7 +2335,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>H6olH5okH5okH5ok</t>
@@ -2431,7 +2352,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>2032871319</t>
@@ -2551,7 +2471,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>75</t>
@@ -2569,7 +2488,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>11915</t>
@@ -2587,7 +2505,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -2605,7 +2522,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -2655,7 +2571,6 @@
           <t>RightAscension</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2673,7 +2588,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2691,7 +2605,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2709,7 +2622,6 @@
           <t>Declination</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2727,7 +2639,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2745,7 +2656,6 @@
           <t>26</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2763,7 +2673,6 @@
           <t>Rotation</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2781,7 +2690,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2799,7 +2707,6 @@
           <t>51</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2829,7 +2736,6 @@
           <t>SDETMETH</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>1</t>
@@ -2847,7 +2753,6 @@
           <t>ATAITIME</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>840068292.008</t>
@@ -2865,7 +2770,6 @@
           <t>AIMMEAN</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>189.042358</t>
@@ -2883,7 +2787,6 @@
           <t>AIMSTD</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>19.295027</t>
@@ -2901,7 +2804,6 @@
           <t>ATHRESH1</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>67</t>
@@ -2919,7 +2821,6 @@
           <t>ATHRESH2</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>48</t>
@@ -2937,7 +2838,6 @@
           <t>AMINELLP</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2955,7 +2855,6 @@
           <t>AMAXELLP</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>0.85</t>
@@ -2973,7 +2872,6 @@
           <t>AMINFLUX</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>7</t>
@@ -2991,7 +2889,6 @@
           <t>AMAXFLUX</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>1600</t>
@@ -3009,7 +2906,6 @@
           <t>AXAXFLIP</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>1</t>
@@ -3027,7 +2923,6 @@
           <t>ASCAL</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>0.7899</t>
@@ -3045,7 +2940,6 @@
           <t>ASCALRMS</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>0.0004</t>
@@ -3063,7 +2957,6 @@
           <t>AROT</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>247.711</t>
@@ -3081,7 +2974,6 @@
           <t>AROTRMS</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>0.032</t>
@@ -3099,7 +2991,6 @@
           <t>ARA</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>307.860376</t>
@@ -3117,7 +3008,6 @@
           <t>ARARMS</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>8.489e-05</t>
@@ -3135,7 +3025,6 @@
           <t>ADEC</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>39.939956</t>
@@ -3153,7 +3042,6 @@
           <t>ADECRMS</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>6.817e-05</t>
@@ -3171,7 +3059,6 @@
           <t>AZERP</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>22.07</t>
@@ -3189,7 +3076,6 @@
           <t>AZERPRMS</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>0.16</t>
@@ -3207,7 +3093,6 @@
           <t>AQUADS</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>73</t>
@@ -3225,7 +3110,6 @@
           <t>AVERTS</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>102</t>
@@ -3243,7 +3127,6 @@
           <t>APHSTARS</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>24</t>
@@ -3261,7 +3144,6 @@
           <t>APOSTARS</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>24</t>
@@ -3279,7 +3161,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>UJK7a9J4XGJ4a9J4</t>
@@ -3297,7 +3178,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>1301764915</t>
@@ -3417,7 +3297,6 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>300</t>
@@ -3435,7 +3314,6 @@
           <t>NAXIS2</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>53</t>
@@ -3453,7 +3331,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3471,7 +3348,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -3521,7 +3397,6 @@
           <t>xCen</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3539,7 +3414,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3557,7 +3431,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3575,7 +3448,6 @@
           <t>yCen</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3593,7 +3465,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3611,7 +3482,6 @@
           <t>26</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3629,7 +3499,6 @@
           <t>Flux</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3647,7 +3516,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3665,7 +3533,6 @@
           <t>51</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3683,7 +3550,6 @@
           <t>Ellipticity</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3701,7 +3567,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3719,7 +3584,6 @@
           <t>76</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3737,7 +3601,6 @@
           <t>NumPix</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3755,7 +3618,6 @@
           <t>I40</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3773,7 +3635,6 @@
           <t>101</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3791,7 +3652,6 @@
           <t>CatalogRA</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3809,7 +3669,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3827,7 +3686,6 @@
           <t>141</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3845,7 +3703,6 @@
           <t>CatalogDec</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3863,7 +3720,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3881,7 +3737,6 @@
           <t>166</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3899,7 +3754,6 @@
           <t>CatalogMag</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3917,7 +3771,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3935,7 +3788,6 @@
           <t>191</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3953,7 +3805,6 @@
           <t>FittedRA</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3971,7 +3822,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3989,7 +3839,6 @@
           <t>216</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4007,7 +3856,6 @@
           <t>FittedDec</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4025,7 +3873,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4043,7 +3890,6 @@
           <t>241</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4061,7 +3907,6 @@
           <t>FittedMag</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4079,7 +3924,6 @@
           <t>D25.17</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4097,7 +3941,6 @@
           <t>266</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4115,7 +3958,6 @@
           <t>CatalogStar</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4133,7 +3975,6 @@
           <t>I10</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4151,7 +3992,6 @@
           <t>291</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4181,7 +4021,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>5PLdAOJa8OJaAOJa</t>
@@ -4199,7 +4038,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>632362844</t>
@@ -4222,7 +4060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4319,13 +4157,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4333,7 +4169,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
@@ -4351,7 +4186,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -4369,7 +4203,6 @@
           <t>FRAME</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>JD</t>
@@ -4406,34 +4239,49 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>TIMEPIXR</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T9lrW7joT7joT7jo</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-09T15:39:21</t>
+          <t>TIME is the middle of each exposure</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>T9lrW7joT7joT7jo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-09-09T15:39:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>1105499181</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>data unit checksum updated 2026-09-09T15:39:21</t>
         </is>
@@ -4547,13 +4395,11 @@
           <t>NAXIS1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4561,7 +4407,6 @@
           <t>PCOUNT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
@@ -4579,7 +4424,6 @@
           <t>GCOUNT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -4597,7 +4441,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>second</t>
@@ -4637,7 +4480,6 @@
           <t>CHECKSUM</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>LlfZMkZZLkfZLkZZ</t>
@@ -4655,7 +4497,6 @@
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>2708996155</t>

--- a/src/pandorafits/formats/visda/level1_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1_visda.xlsx
@@ -4222,7 +4222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4436,6 +4436,28 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>data unit checksum updated 2026-09-09T15:39:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TIMESYS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>UTC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Time scale</t>
         </is>
       </c>
     </row>
